--- a/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-patient-explanation.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-patient-explanation.xlsx
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>EU AI Act Patient Right to Explanation</t>
+    <t>EU AI Patient Explanation Communication</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T08:40:47+00:00</t>
+    <t>2026-06-18T12:04:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Documents the fulfillment of the patient's right to a clear and meaningful explanation regarding the AI's role and the clinical decision (LAW-07).</t>
+    <t>A Communication profile documenting patient-facing information about the AI-supported workflow, including the role of the AI system and the related clinical review where applicable.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -861,7 +861,7 @@
     <t>Communication.sender</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole)
+    <t xml:space="preserve">Reference(PractitionerRole)
 </t>
   </si>
   <si>

--- a/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-patient-explanation.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-patient-explanation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$36</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1324" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1291" uniqueCount="301">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T12:04:51+00:00</t>
+    <t>2026-07-31T11:07:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>A Communication profile documenting patient-facing information about the AI-supported workflow, including the role of the AI system and the related clinical review where applicable.</t>
+    <t>A Communication profile documenting that an explanation regarding an AI-supported clinical decision was provided to a patient. The explanation may describe the role of the AI system, the related human oversight, and the key elements of the resulting clinical decision in accordance with Article 86 of the EU AI Act.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -424,21 +424,21 @@
     <t>Communication.extension</t>
   </si>
   <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
     <t xml:space="preserve">Extension
 </t>
   </si>
   <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>open</t>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t>DomainResource.extension</t>
@@ -448,27 +448,7 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>Communication.extension:explanationRequested</t>
-  </si>
-  <si>
-    <t>explanationRequested</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://example.org/fhir/eu-ai-transparency/StructureDefinition/eu-ai-explanation-requested}
-</t>
-  </si>
-  <si>
-    <t>Flag: Did the patient/data subject actively request this explanation?</t>
-  </si>
-  <si>
-    <t>Flag indicating if the patient (data subject) explicitly requested a clear and meaningful explanation of the AI's role and the clinical decision.</t>
-  </si>
-  <si>
     <t>Communication.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user content</t>
   </si>
   <si>
     <t>Extensions that cannot be ignored</t>
@@ -478,9 +458,6 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R5/extensibility.html#modifierExtension).</t>
   </si>
   <si>
@@ -604,7 +581,7 @@
     <t>Communication.status</t>
   </si>
   <si>
-    <t>preparation | in-progress | completed | not-done</t>
+    <t>preparation | in-progress | not-done | on-hold | stopped | completed | entered-in-error | unknown</t>
   </si>
   <si>
     <t>The status of the transmission.</t>
@@ -669,15 +646,6 @@
     <t>There may be multiple axes of categorization and one communication may serve multiple purposes.</t>
   </si>
   <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;system value="http://terminology.hl7.org/CodeSystem/communication-category"/&gt;
-    &lt;code value="instruction"/&gt;
-    &lt;display value="Instruction"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
-  </si>
-  <si>
     <t>Codes for general categories of communications such as alerts, instructions, etc.</t>
   </si>
   <si>
@@ -773,14 +741,10 @@
     <t>Communication.about</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://example.org/fhir/eu-ai-transparency/StructureDefinition/eu-ai-human-oversight)
-</t>
-  </si>
-  <si>
     <t>The specific decision the patient wants to have explained</t>
   </si>
   <si>
-    <t>Other resources that pertain to this communication and to which this communication should be associated.</t>
+    <t>References the AI-generated or AI-supported clinical output, related human oversight assessment, provenance record, or other resource representing the decision or workflow addressed by the patient-facing explanation.</t>
   </si>
   <si>
     <t>Don't use Communication.about element when a more specific element exists, such as basedOn or reasonReference.</t>
@@ -909,7 +873,7 @@
 </t>
   </si>
   <si>
-    <t>The explanation text OR a reference to a formal explanation document</t>
+    <t>Patient-facing explanation or reference to an explanation document</t>
   </si>
   <si>
     <t>Text, attachment(s), or resource(s) that was communicated to the recipient.</t>
@@ -941,9 +905,6 @@
     <t>Communication.payload.extension</t>
   </si>
   <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
@@ -970,8 +931,8 @@
     <t>Communication.payload.content[x]</t>
   </si>
   <si>
-    <t>Reference(DocumentReference)
-CodeableConcept</t>
+    <t>Attachment
+Reference(DocumentReference)</t>
   </si>
   <si>
     <t>Message part content</t>
@@ -1307,12 +1268,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM37"/>
+  <dimension ref="A1:AM36"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="39.6875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="34.78125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="34.78125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="18.578125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -2251,11 +2212,11 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>18</v>
+        <v>131</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="G9" t="s" s="2">
         <v>75</v>
@@ -2270,15 +2231,17 @@
         <v>18</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="N9" s="2"/>
+        <v>134</v>
+      </c>
+      <c r="N9" t="s" s="2">
+        <v>135</v>
+      </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>18</v>
@@ -2315,14 +2278,16 @@
         <v>18</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AC9" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>18</v>
+      </c>
       <c r="AD9" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>135</v>
+        <v>18</v>
       </c>
       <c r="AF9" t="s" s="2">
         <v>136</v>
@@ -2346,49 +2311,51 @@
         <v>18</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>138</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="C10" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>18</v>
+        <v>131</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="H10" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I10" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="I10" t="s" s="2">
-        <v>18</v>
-      </c>
       <c r="J10" t="s" s="2">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L10" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="M10" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="L10" t="s" s="2">
+      <c r="N10" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="O10" t="s" s="2">
         <v>141</v>
       </c>
-      <c r="M10" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>18</v>
       </c>
@@ -2436,7 +2403,7 @@
         <v>18</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
@@ -2457,7 +2424,7 @@
         <v>18</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>18</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11" hidden="true">
@@ -2469,7 +2436,7 @@
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>144</v>
+        <v>18</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -2482,13 +2449,13 @@
         <v>18</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="L11" t="s" s="2">
         <v>145</v>
@@ -2549,7 +2516,7 @@
         <v>18</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>74</v>
@@ -2561,24 +2528,24 @@
         <v>18</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>137</v>
+        <v>96</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>18</v>
+        <v>149</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>18</v>
+        <v>150</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>129</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2601,20 +2568,16 @@
         <v>85</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N12" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="O12" t="s" s="2">
-        <v>155</v>
-      </c>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>18</v>
       </c>
@@ -2662,7 +2625,7 @@
         <v>18</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
@@ -2677,21 +2640,21 @@
         <v>96</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM12" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="AL12" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>18</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2714,15 +2677,17 @@
         <v>85</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M13" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="M13" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>18</v>
@@ -2771,7 +2736,7 @@
         <v>18</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
@@ -2786,25 +2751,25 @@
         <v>96</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>18</v>
+        <v>163</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -2823,7 +2788,7 @@
         <v>85</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>98</v>
+        <v>164</v>
       </c>
       <c r="L14" t="s" s="2">
         <v>165</v>
@@ -2882,7 +2847,7 @@
         <v>18</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
@@ -2903,7 +2868,7 @@
         <v>18</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>163</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" hidden="true">
@@ -2934,16 +2899,16 @@
         <v>85</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3008,7 +2973,7 @@
         <v>96</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>18</v>
@@ -3019,14 +2984,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>177</v>
+        <v>18</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3042,20 +3007,18 @@
         <v>18</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="M16" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>180</v>
-      </c>
+      <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>18</v>
@@ -3104,7 +3067,7 @@
         <v>18</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>74</v>
@@ -3119,7 +3082,7 @@
         <v>96</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>181</v>
+        <v>18</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>18</v>
@@ -3130,10 +3093,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3141,30 +3104,32 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>183</v>
+        <v>104</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="N17" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>18</v>
@@ -3189,13 +3154,13 @@
         <v>18</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>18</v>
+        <v>108</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>18</v>
+        <v>183</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>18</v>
+        <v>184</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>18</v>
@@ -3213,13 +3178,13 @@
         <v>18</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>18</v>
@@ -3228,53 +3193,53 @@
         <v>96</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>18</v>
+        <v>185</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>18</v>
+        <v>186</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>18</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>18</v>
+        <v>188</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="J18" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>104</v>
+        <v>189</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3300,13 +3265,13 @@
         <v>18</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>108</v>
+        <v>193</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>18</v>
@@ -3324,10 +3289,10 @@
         <v>18</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="AH18" t="s" s="2">
         <v>84</v>
@@ -3339,10 +3304,10 @@
         <v>96</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>193</v>
+        <v>18</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>18</v>
@@ -3350,21 +3315,21 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>195</v>
+        <v>18</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>18</v>
@@ -3373,19 +3338,19 @@
         <v>18</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3411,7 +3376,7 @@
         <v>18</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="Y19" t="s" s="2">
         <v>201</v>
@@ -3435,13 +3400,13 @@
         <v>18</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>18</v>
@@ -3450,10 +3415,10 @@
         <v>96</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL19" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="AL19" t="s" s="2">
-        <v>18</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>18</v>
@@ -3475,7 +3440,7 @@
         <v>74</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>18</v>
@@ -3484,10 +3449,10 @@
         <v>18</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>196</v>
+        <v>104</v>
       </c>
       <c r="L20" t="s" s="2">
         <v>205</v>
@@ -3502,12 +3467,14 @@
       <c r="P20" t="s" s="2">
         <v>18</v>
       </c>
-      <c r="Q20" s="2"/>
+      <c r="Q20" t="s" s="2">
+        <v>208</v>
+      </c>
       <c r="R20" t="s" s="2">
         <v>18</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>18</v>
@@ -3522,7 +3489,7 @@
         <v>18</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>200</v>
+        <v>108</v>
       </c>
       <c r="Y20" t="s" s="2">
         <v>209</v>
@@ -3552,7 +3519,7 @@
         <v>74</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>18</v>
@@ -3586,7 +3553,7 @@
         <v>74</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>18</v>
@@ -3595,10 +3562,10 @@
         <v>18</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>104</v>
+        <v>189</v>
       </c>
       <c r="L21" t="s" s="2">
         <v>213</v>
@@ -3606,42 +3573,38 @@
       <c r="M21" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="N21" t="s" s="2">
-        <v>215</v>
-      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>18</v>
       </c>
-      <c r="Q21" t="s" s="2">
+      <c r="Q21" s="2"/>
+      <c r="R21" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="S21" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="T21" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U21" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V21" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W21" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X21" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="Z21" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="R21" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="S21" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="T21" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="U21" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="V21" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="W21" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="X21" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="Y21" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="Z21" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>18</v>
@@ -3665,7 +3628,7 @@
         <v>74</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>18</v>
@@ -3677,47 +3640,47 @@
         <v>18</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>219</v>
+        <v>18</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>18</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>18</v>
+        <v>218</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>18</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3744,13 +3707,13 @@
         <v>18</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>200</v>
+        <v>18</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>223</v>
+        <v>18</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>224</v>
+        <v>18</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>18</v>
@@ -3768,13 +3731,13 @@
         <v>18</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>18</v>
@@ -3783,52 +3746,54 @@
         <v>96</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>18</v>
+        <v>222</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>18</v>
+        <v>223</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>18</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>226</v>
+        <v>18</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>18</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="M23" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="N23" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="L23" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>18</v>
@@ -3853,13 +3818,13 @@
         <v>18</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>18</v>
+        <v>193</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>18</v>
+        <v>228</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>18</v>
+        <v>229</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>18</v>
@@ -3877,7 +3842,7 @@
         <v>18</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
@@ -3892,21 +3857,21 @@
         <v>96</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL23" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="AL23" t="s" s="2">
+      <c r="AM23" t="s" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="AM23" t="s" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="24" hidden="true">
-      <c r="A24" t="s" s="2">
-        <v>232</v>
-      </c>
       <c r="B24" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3914,13 +3879,13 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>18</v>
@@ -3929,16 +3894,16 @@
         <v>18</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>196</v>
+        <v>164</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -3964,13 +3929,13 @@
         <v>18</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>200</v>
+        <v>18</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>236</v>
+        <v>18</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>237</v>
+        <v>18</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>18</v>
@@ -3988,13 +3953,13 @@
         <v>18</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>18</v>
@@ -4006,18 +3971,18 @@
         <v>18</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>18</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4025,31 +3990,31 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G25" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="G25" t="s" s="2">
-        <v>75</v>
-      </c>
       <c r="H25" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J25" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="I25" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J25" t="s" s="2">
-        <v>18</v>
-      </c>
       <c r="K25" t="s" s="2">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4099,13 +4064,13 @@
         <v>18</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>18</v>
@@ -4114,21 +4079,21 @@
         <v>96</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>18</v>
+        <v>240</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>18</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4136,32 +4101,30 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>18</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>248</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>18</v>
@@ -4210,7 +4173,7 @@
         <v>18</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>74</v>
@@ -4225,21 +4188,21 @@
         <v>96</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>18</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4247,13 +4210,13 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>18</v>
@@ -4262,13 +4225,13 @@
         <v>18</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4319,7 +4282,7 @@
         <v>18</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>
@@ -4334,10 +4297,10 @@
         <v>96</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>18</v>
@@ -4345,10 +4308,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4359,7 +4322,7 @@
         <v>74</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>18</v>
@@ -4371,15 +4334,17 @@
         <v>18</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>254</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>255</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>18</v>
@@ -4428,13 +4393,13 @@
         <v>18</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>18</v>
@@ -4443,21 +4408,21 @@
         <v>96</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>18</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4465,13 +4430,13 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>18</v>
@@ -4480,17 +4445,15 @@
         <v>18</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="L29" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>264</v>
-      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>18</v>
@@ -4539,13 +4502,13 @@
         <v>18</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>18</v>
@@ -4554,21 +4517,21 @@
         <v>96</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>18</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4576,30 +4539,32 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="H30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J30" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="I30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J30" t="s" s="2">
-        <v>18</v>
-      </c>
       <c r="K30" t="s" s="2">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>265</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>266</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>18</v>
@@ -4624,13 +4589,13 @@
         <v>18</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>18</v>
+        <v>193</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>18</v>
+        <v>267</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>18</v>
+        <v>268</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>18</v>
@@ -4648,13 +4613,13 @@
         <v>18</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>18</v>
@@ -4663,21 +4628,21 @@
         <v>96</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="31" hidden="true">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="31">
       <c r="A31" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4685,32 +4650,30 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>18</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N31" t="s" s="2">
         <v>275</v>
       </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>18</v>
@@ -4735,13 +4698,13 @@
         <v>18</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>200</v>
+        <v>18</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>276</v>
+        <v>18</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>277</v>
+        <v>18</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>18</v>
@@ -4759,7 +4722,7 @@
         <v>18</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
@@ -4774,21 +4737,21 @@
         <v>96</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>278</v>
+        <v>18</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>279</v>
+        <v>18</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="32">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4796,13 +4759,13 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G32" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="G32" t="s" s="2">
-        <v>75</v>
-      </c>
       <c r="H32" t="s" s="2">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>18</v>
@@ -4811,13 +4774,13 @@
         <v>18</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4868,19 +4831,19 @@
         <v>18</v>
       </c>
       <c r="AF32" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI32" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="AG32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH32" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI32" t="s" s="2">
-        <v>18</v>
-      </c>
       <c r="AJ32" t="s" s="2">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>18</v>
@@ -4889,26 +4852,26 @@
         <v>18</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>18</v>
+        <v>282</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>18</v>
+        <v>131</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>18</v>
@@ -4920,15 +4883,17 @@
         <v>18</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>286</v>
+        <v>132</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>287</v>
+        <v>133</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>284</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>135</v>
+      </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>18</v>
@@ -4977,19 +4942,19 @@
         <v>18</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>290</v>
+        <v>18</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>18</v>
+        <v>137</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>18</v>
@@ -4998,19 +4963,19 @@
         <v>18</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>291</v>
+        <v>282</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>144</v>
+        <v>287</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5023,24 +4988,26 @@
         <v>18</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="O34" s="2"/>
+        <v>135</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>141</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>18</v>
       </c>
@@ -5088,7 +5055,7 @@
         <v>18</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>74</v>
@@ -5109,51 +5076,49 @@
         <v>18</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>291</v>
+        <v>129</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>297</v>
+        <v>18</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>131</v>
+        <v>292</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>148</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>18</v>
       </c>
@@ -5201,19 +5166,19 @@
         <v>18</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>137</v>
+        <v>96</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>18</v>
@@ -5222,15 +5187,15 @@
         <v>18</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>129</v>
+        <v>18</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5238,10 +5203,10 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>18</v>
@@ -5253,17 +5218,15 @@
         <v>18</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>305</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>18</v>
@@ -5312,13 +5275,13 @@
         <v>18</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>18</v>
@@ -5327,7 +5290,7 @@
         <v>96</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>18</v>
+        <v>300</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>18</v>
@@ -5336,117 +5299,8 @@
         <v>18</v>
       </c>
     </row>
-    <row r="37" hidden="true">
-      <c r="A37" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="B37" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="C37" s="2"/>
-      <c r="D37" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="E37" s="2"/>
-      <c r="F37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G37" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H37" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I37" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J37" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="K37" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="L37" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
-      <c r="P37" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Q37" s="2"/>
-      <c r="R37" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="S37" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="T37" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="U37" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="V37" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="W37" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="X37" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Y37" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Z37" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AA37" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB37" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD37" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE37" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF37" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="AG37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH37" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI37" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AJ37" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AK37" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="AL37" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>18</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AM37">
+  <autoFilter ref="A1:AM36">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -5456,7 +5310,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI36">
+  <conditionalFormatting sqref="A2:AI35">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-patient-explanation.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-patient-explanation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T11:07:29+00:00</t>
+    <t>2026-09-02T10:48:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-patient-explanation.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-patient-explanation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$37</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1291" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1324" uniqueCount="309">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T10:48:14+00:00</t>
+    <t>2026-09-03T11:53:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -424,33 +424,53 @@
     <t>Communication.extension</t>
   </si>
   <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Communication.extension:aifInfoProvided</t>
+  </si>
+  <si>
+    <t>aifInfoProvided</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://example.org/fhir/eu-ai-transparency/StructureDefinition/patient-ai-info-provided-flag}
+</t>
+  </si>
+  <si>
+    <t>Flag if the patient was informed about the use of AI.</t>
+  </si>
+  <si>
+    <t>This flag represents whether the patient has been informed about the AI-related processing activity</t>
+  </si>
+  <si>
+    <t>Communication.modifierExtension</t>
+  </si>
+  <si>
     <t>extensions
 user content</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>Communication.modifierExtension</t>
-  </si>
-  <si>
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
@@ -458,6 +478,9 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R5/extensibility.html#modifierExtension).</t>
   </si>
   <si>
@@ -903,6 +926,9 @@
   </si>
   <si>
     <t>Communication.payload.extension</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
@@ -1268,12 +1294,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM36"/>
+  <dimension ref="A1:AM37"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="34.78125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="34.78125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="12.70703125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -2212,11 +2238,11 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>131</v>
+        <v>18</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="G9" t="s" s="2">
         <v>75</v>
@@ -2231,17 +2257,15 @@
         <v>18</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>132</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="M9" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>135</v>
-      </c>
+      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>18</v>
@@ -2278,16 +2302,14 @@
         <v>18</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>18</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>18</v>
+        <v>135</v>
       </c>
       <c r="AF9" t="s" s="2">
         <v>136</v>
@@ -2311,51 +2333,49 @@
         <v>18</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="10" hidden="true">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>138</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="C10" s="2"/>
+        <v>130</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="D10" t="s" s="2">
-        <v>131</v>
+        <v>18</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>141</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>18</v>
       </c>
@@ -2403,7 +2423,7 @@
         <v>18</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
@@ -2424,7 +2444,7 @@
         <v>18</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>129</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" hidden="true">
@@ -2436,7 +2456,7 @@
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>18</v>
+        <v>144</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -2449,13 +2469,13 @@
         <v>18</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="L11" t="s" s="2">
         <v>145</v>
@@ -2516,7 +2536,7 @@
         <v>18</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>74</v>
@@ -2528,24 +2548,24 @@
         <v>18</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>96</v>
+        <v>137</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>149</v>
+        <v>18</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>150</v>
+        <v>18</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>18</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2568,16 +2588,20 @@
         <v>85</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="M12" t="s" s="2">
+      <c r="N12" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
+      <c r="O12" t="s" s="2">
+        <v>155</v>
+      </c>
       <c r="P12" t="s" s="2">
         <v>18</v>
       </c>
@@ -2625,7 +2649,7 @@
         <v>18</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
@@ -2640,21 +2664,21 @@
         <v>96</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>18</v>
+        <v>157</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>156</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2677,17 +2701,15 @@
         <v>85</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>160</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>18</v>
@@ -2736,7 +2758,7 @@
         <v>18</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
@@ -2751,25 +2773,25 @@
         <v>96</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>156</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>163</v>
+        <v>18</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -2788,7 +2810,7 @@
         <v>85</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>164</v>
+        <v>98</v>
       </c>
       <c r="L14" t="s" s="2">
         <v>165</v>
@@ -2847,7 +2869,7 @@
         <v>18</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
@@ -2868,7 +2890,7 @@
         <v>18</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>18</v>
+        <v>163</v>
       </c>
     </row>
     <row r="15" hidden="true">
@@ -2899,16 +2921,16 @@
         <v>85</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -2973,7 +2995,7 @@
         <v>96</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>18</v>
@@ -2984,14 +3006,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>18</v>
+        <v>177</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3007,18 +3029,20 @@
         <v>18</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N16" s="2"/>
+        <v>179</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>180</v>
+      </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>18</v>
@@ -3067,7 +3091,7 @@
         <v>18</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>74</v>
@@ -3082,7 +3106,7 @@
         <v>96</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>18</v>
+        <v>181</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>18</v>
@@ -3093,10 +3117,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3104,32 +3128,30 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>104</v>
+        <v>183</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>182</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>18</v>
@@ -3154,13 +3176,13 @@
         <v>18</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>108</v>
+        <v>18</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>183</v>
+        <v>18</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>184</v>
+        <v>18</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>18</v>
@@ -3178,13 +3200,13 @@
         <v>18</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>18</v>
@@ -3193,10 +3215,10 @@
         <v>96</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>185</v>
+        <v>18</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>186</v>
+        <v>18</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>18</v>
@@ -3204,18 +3226,18 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>188</v>
+        <v>18</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>84</v>
@@ -3224,22 +3246,22 @@
         <v>18</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="J18" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="N18" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="L18" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>192</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3265,13 +3287,13 @@
         <v>18</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>193</v>
+        <v>108</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>18</v>
@@ -3289,10 +3311,10 @@
         <v>18</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="AH18" t="s" s="2">
         <v>84</v>
@@ -3304,10 +3326,10 @@
         <v>96</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>18</v>
+        <v>193</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>18</v>
@@ -3315,21 +3337,21 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>18</v>
+        <v>195</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>18</v>
@@ -3338,19 +3360,19 @@
         <v>18</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3376,7 +3398,7 @@
         <v>18</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="Y19" t="s" s="2">
         <v>201</v>
@@ -3400,13 +3422,13 @@
         <v>18</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>18</v>
@@ -3415,10 +3437,10 @@
         <v>96</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>18</v>
+        <v>203</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>203</v>
+        <v>18</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>18</v>
@@ -3440,7 +3462,7 @@
         <v>74</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>18</v>
@@ -3449,10 +3471,10 @@
         <v>18</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>104</v>
+        <v>196</v>
       </c>
       <c r="L20" t="s" s="2">
         <v>205</v>
@@ -3467,35 +3489,33 @@
       <c r="P20" t="s" s="2">
         <v>18</v>
       </c>
-      <c r="Q20" t="s" s="2">
+      <c r="Q20" s="2"/>
+      <c r="R20" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="S20" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="T20" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U20" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V20" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W20" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X20" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="Y20" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="R20" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="S20" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="T20" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="U20" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="V20" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="W20" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="X20" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="Y20" t="s" s="2">
+      <c r="Z20" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="Z20" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>18</v>
@@ -3519,7 +3539,7 @@
         <v>74</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>18</v>
@@ -3531,7 +3551,7 @@
         <v>18</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>18</v>
@@ -3539,10 +3559,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3553,7 +3573,7 @@
         <v>74</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>18</v>
@@ -3562,23 +3582,27 @@
         <v>18</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>189</v>
+        <v>104</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>18</v>
       </c>
-      <c r="Q21" s="2"/>
+      <c r="Q21" t="s" s="2">
+        <v>215</v>
+      </c>
       <c r="R21" t="s" s="2">
         <v>18</v>
       </c>
@@ -3598,13 +3622,13 @@
         <v>18</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>193</v>
+        <v>108</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>18</v>
@@ -3622,13 +3646,13 @@
         <v>18</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>18</v>
@@ -3640,41 +3664,41 @@
         <v>18</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>18</v>
+        <v>218</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>18</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>218</v>
+        <v>18</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>18</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>219</v>
+        <v>196</v>
       </c>
       <c r="L22" t="s" s="2">
         <v>220</v>
@@ -3707,13 +3731,13 @@
         <v>18</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>18</v>
+        <v>200</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>18</v>
+        <v>222</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>18</v>
+        <v>223</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>18</v>
@@ -3731,13 +3755,13 @@
         <v>18</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>18</v>
@@ -3746,16 +3770,16 @@
         <v>96</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>222</v>
+        <v>18</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>223</v>
+        <v>18</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>18</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
         <v>224</v>
       </c>
@@ -3764,36 +3788,34 @@
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>18</v>
+        <v>225</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>18</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>189</v>
+        <v>226</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>227</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>18</v>
@@ -3818,13 +3840,13 @@
         <v>18</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>193</v>
+        <v>18</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>228</v>
+        <v>18</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>229</v>
+        <v>18</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>18</v>
@@ -3857,7 +3879,7 @@
         <v>96</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>18</v>
+        <v>229</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>230</v>
@@ -3866,7 +3888,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
         <v>231</v>
       </c>
@@ -3879,13 +3901,13 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G24" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="G24" t="s" s="2">
-        <v>75</v>
-      </c>
       <c r="H24" t="s" s="2">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>18</v>
@@ -3894,7 +3916,7 @@
         <v>18</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>164</v>
+        <v>196</v>
       </c>
       <c r="L24" t="s" s="2">
         <v>232</v>
@@ -3929,13 +3951,13 @@
         <v>18</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>18</v>
+        <v>200</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>18</v>
+        <v>235</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>18</v>
+        <v>236</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>18</v>
@@ -3959,7 +3981,7 @@
         <v>74</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>18</v>
@@ -3971,18 +3993,18 @@
         <v>18</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>18</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3990,31 +4012,31 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>18</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>236</v>
+        <v>171</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4064,13 +4086,13 @@
         <v>18</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>18</v>
@@ -4079,21 +4101,21 @@
         <v>96</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>240</v>
+        <v>18</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>18</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4101,30 +4123,32 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H26" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I26" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J26" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="I26" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J26" t="s" s="2">
-        <v>18</v>
-      </c>
       <c r="K26" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>245</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>18</v>
@@ -4173,7 +4197,7 @@
         <v>18</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>74</v>
@@ -4188,21 +4212,21 @@
         <v>96</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>18</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4210,13 +4234,13 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>18</v>
@@ -4225,13 +4249,13 @@
         <v>18</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4282,7 +4306,7 @@
         <v>18</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>
@@ -4297,10 +4321,10 @@
         <v>96</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>18</v>
@@ -4308,10 +4332,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4322,7 +4346,7 @@
         <v>74</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>18</v>
@@ -4334,17 +4358,15 @@
         <v>18</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>255</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>18</v>
@@ -4393,13 +4415,13 @@
         <v>18</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>18</v>
@@ -4408,16 +4430,16 @@
         <v>96</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>18</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
         <v>258</v>
       </c>
@@ -4430,13 +4452,13 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>18</v>
@@ -4453,7 +4475,9 @@
       <c r="M29" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="N29" s="2"/>
+      <c r="N29" t="s" s="2">
+        <v>262</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>18</v>
@@ -4508,7 +4532,7 @@
         <v>74</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>18</v>
@@ -4517,21 +4541,21 @@
         <v>96</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>18</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4539,32 +4563,30 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>18</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>266</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>18</v>
@@ -4589,13 +4611,13 @@
         <v>18</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>193</v>
+        <v>18</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>267</v>
+        <v>18</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>268</v>
+        <v>18</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>18</v>
@@ -4613,13 +4635,13 @@
         <v>18</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>18</v>
@@ -4628,21 +4650,21 @@
         <v>96</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31" hidden="true">
+      <c r="A31" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="AL30" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s" s="2">
-        <v>272</v>
-      </c>
       <c r="B31" t="s" s="2">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4650,30 +4672,32 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J31" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="I31" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J31" t="s" s="2">
-        <v>18</v>
-      </c>
       <c r="K31" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="N31" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="L31" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>18</v>
@@ -4698,13 +4722,13 @@
         <v>18</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>18</v>
+        <v>200</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>18</v>
+        <v>274</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>18</v>
+        <v>275</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>18</v>
@@ -4722,7 +4746,7 @@
         <v>18</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
@@ -4737,21 +4761,21 @@
         <v>96</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>18</v>
+        <v>276</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>18</v>
+        <v>277</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="32" hidden="true">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="32">
       <c r="A32" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4759,13 +4783,13 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>18</v>
@@ -4774,13 +4798,13 @@
         <v>18</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4831,19 +4855,19 @@
         <v>18</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>281</v>
+        <v>18</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>18</v>
+        <v>96</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>18</v>
@@ -4852,7 +4876,7 @@
         <v>18</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>282</v>
+        <v>18</v>
       </c>
     </row>
     <row r="33" hidden="true">
@@ -4864,14 +4888,14 @@
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>131</v>
+        <v>18</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>18</v>
@@ -4883,17 +4907,15 @@
         <v>18</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>132</v>
+        <v>284</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>133</v>
+        <v>285</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>135</v>
-      </c>
+        <v>286</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>18</v>
@@ -4942,19 +4964,19 @@
         <v>18</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>18</v>
+        <v>288</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>137</v>
+        <v>18</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>18</v>
@@ -4963,19 +4985,19 @@
         <v>18</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>282</v>
+        <v>289</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>287</v>
+        <v>144</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -4988,26 +5010,24 @@
         <v>18</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>141</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>18</v>
       </c>
@@ -5055,7 +5075,7 @@
         <v>18</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>74</v>
@@ -5076,49 +5096,51 @@
         <v>18</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>129</v>
+        <v>289</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>18</v>
+        <v>295</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>292</v>
+        <v>131</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="O35" s="2"/>
+        <v>147</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>18</v>
       </c>
@@ -5166,19 +5188,19 @@
         <v>18</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>96</v>
+        <v>137</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>18</v>
@@ -5187,15 +5209,15 @@
         <v>18</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>18</v>
+        <v>129</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5203,10 +5225,10 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>18</v>
@@ -5218,15 +5240,17 @@
         <v>18</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>302</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>303</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>18</v>
@@ -5275,13 +5299,13 @@
         <v>18</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>18</v>
@@ -5290,7 +5314,7 @@
         <v>96</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>300</v>
+        <v>18</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>18</v>
@@ -5299,8 +5323,117 @@
         <v>18</v>
       </c>
     </row>
+    <row r="37" hidden="true">
+      <c r="A37" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="E37" s="2"/>
+      <c r="F37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J37" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="K37" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
+      <c r="P37" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Q37" s="2"/>
+      <c r="R37" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="S37" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF37" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>18</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AM36">
+  <autoFilter ref="A1:AM37">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -5310,7 +5443,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI35">
+  <conditionalFormatting sqref="A2:AI36">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-patient-explanation.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-patient-explanation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T11:53:05+00:00</t>
+    <t>2026-09-07T08:39:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
